--- a/data/trans_camb/P1417-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1417-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,26</t>
+          <t>-0,19; 1,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,0</t>
+          <t>-0,78; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,96</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,68</t>
+          <t>0,3; 2,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 8,18</t>
+          <t>0,61; 6,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,91</t>
+          <t>-0,18; 0,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,69</t>
+          <t>0,18; 1,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,7</t>
+          <t>0,1; 2,69</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1415,11%</t>
+          <t>1260,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>569,01%</t>
+          <t>543,92%</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,79; —</t>
+          <t>4,79; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,42</t>
+          <t>-0,27; 0,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,68</t>
+          <t>-0,27; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,89</t>
+          <t>-0,94; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,0</t>
+          <t>-0,92; 1,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,72</t>
+          <t>-0,78; 2,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,84</t>
+          <t>-0,56; 0,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,02</t>
+          <t>-0,47; 1,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,39</t>
+          <t>-0,34; 1,31</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 241,89</t>
+          <t>-52,55; 225,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 232,25</t>
+          <t>-50,62; 236,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 323,07</t>
+          <t>-43,47; 298,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 190,87</t>
+          <t>-57,49; 198,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 224,77</t>
+          <t>-46,55; 243,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 314,02</t>
+          <t>-39,71; 289,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,46</t>
+          <t>-0,28; 0,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,95</t>
+          <t>-0,28; 0,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,22</t>
+          <t>0,08; 1,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,86</t>
+          <t>0,43; 4,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,91</t>
+          <t>-1,05; 1,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,93</t>
+          <t>2,08; 5,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,09</t>
+          <t>0,16; 2,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,98</t>
+          <t>-0,58; 0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,51</t>
+          <t>1,31; 3,37</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>659,78%</t>
+          <t>569,46%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>210,49%</t>
+          <t>218,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>232,59%</t>
+          <t>232,33%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 356,5</t>
+          <t>11,38; 361,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,49; 185,64</t>
+          <t>-45,33; 193,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,37; 528,93</t>
+          <t>68,2; 564,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 341,5</t>
+          <t>3,81; 329,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 155,35</t>
+          <t>-44,31; 171,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,21; 611,15</t>
+          <t>79,51; 592,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>2,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,05</t>
+          <t>-0,55; 0,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,8</t>
+          <t>-0,57; 0,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,51</t>
+          <t>-0,53; 0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,08</t>
+          <t>-0,35; 2,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,56</t>
+          <t>-0,68; 2,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,67</t>
+          <t>2,77; 6,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,57</t>
+          <t>-0,13; 1,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,34</t>
+          <t>-0,31; 1,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,73</t>
+          <t>1,47; 3,4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-11,28%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>311,05%</t>
+          <t>337,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>210,28%</t>
+          <t>285,93%</t>
         </is>
       </c>
     </row>
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 426,29</t>
+          <t>-28,66; 430,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,35; 359,06</t>
+          <t>-39,46; 359,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,62; 814,08</t>
+          <t>112,25; 981,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 341,12</t>
+          <t>-16,83; 353,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 281,19</t>
+          <t>-29,95; 289,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>53,67; 633,67</t>
+          <t>101,69; 783,74</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,63</t>
+          <t>0,91; 2,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,2</t>
+          <t>-1,54; 2,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,4</t>
+          <t>-1,71; 2,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,93</t>
+          <t>-1,58; 2,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,58</t>
+          <t>-0,69; 1,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,43</t>
+          <t>-0,78; 1,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,84</t>
+          <t>-0,2; 1,9</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 163,35</t>
+          <t>-52,39; 199,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 204,24</t>
+          <t>-55,97; 213,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 160,42</t>
+          <t>-44,35; 174,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 250,25</t>
+          <t>-47,31; 226,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 209,07</t>
+          <t>-51,69; 223,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 292,21</t>
+          <t>-14,23; 279,66</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,6</t>
+          <t>-1,73; 2,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,83</t>
+          <t>-2,11; 1,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,39</t>
+          <t>-0,9; 3,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,69</t>
+          <t>-0,9; 3,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,24</t>
+          <t>-1,16; 3,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,04</t>
+          <t>-0,72; 3,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,65</t>
+          <t>-0,7; 2,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,17</t>
+          <t>-0,91; 2,06</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,02</t>
+          <t>-0,14; 2,6</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-80,55; 504,11</t>
+          <t>-80,94; 529,85</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,07; 373,5</t>
+          <t>-86,97; 430,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 669,97</t>
+          <t>-40,72; 666,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-48,14; 366,63</t>
+          <t>-40,71; 376,23</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 319,14</t>
+          <t>-47,27; 379,92</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,51; 181,31</t>
+          <t>-26,23; 357,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 263,89</t>
+          <t>-35,57; 273,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 196,72</t>
+          <t>-42,93; 212,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 198,66</t>
+          <t>-9,21; 276,11</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,74</t>
+          <t>-4,02; 0,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,77</t>
+          <t>-3,46; 1,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,63</t>
+          <t>-0,98; 4,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,34</t>
+          <t>-3,09; 3,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,76</t>
+          <t>-2,86; 3,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,82</t>
+          <t>1,93; 7,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,63</t>
+          <t>-2,52; 1,82</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,12</t>
+          <t>-1,97; 2,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,83</t>
+          <t>1,38; 5,72</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>104,29%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>127,03%</t>
+          <t>124,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>118,0%</t>
+          <t>117,67%</t>
         </is>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,64; 311,94</t>
+          <t>-92,71; 270,92</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 693,07</t>
+          <t>-36,55; 555,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 157,99</t>
+          <t>-57,04; 136,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 183,21</t>
+          <t>-50,94; 143,41</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,99; 385,76</t>
+          <t>26,49; 357,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 89,79</t>
+          <t>-58,09; 97,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 96,42</t>
+          <t>-46,97; 116,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>29,29; 318,99</t>
+          <t>22,13; 276,51</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,32</t>
+          <t>-0,29; 0,36</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,49</t>
+          <t>-0,21; 0,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,1</t>
+          <t>0,45; 1,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,72</t>
+          <t>0,29; 1,72</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,5</t>
+          <t>0,06; 1,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,37</t>
+          <t>2,06; 3,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,91</t>
+          <t>0,16; 0,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,87</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,07</t>
+          <t>1,44; 2,3</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>172,7%</t>
+          <t>201,49%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>145,44%</t>
+          <t>164,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>152,42%</t>
+          <t>173,61%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 128,77</t>
+          <t>-52,01; 141,41</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 186,55</t>
+          <t>-41,02; 184,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>39,29; 445,22</t>
+          <t>62,96; 473,84</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,85; 122,3</t>
+          <t>12,48; 121,35</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,4; 111,45</t>
+          <t>1,59; 103,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>76,31; 246,6</t>
+          <t>100,35; 265,53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,66; 102,72</t>
+          <t>11,62; 104,37</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,58; 97,22</t>
+          <t>6,17; 97,85</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>88,57; 234,71</t>
+          <t>108,79; 262,21</t>
         </is>
       </c>
     </row>
